--- a/docs/Logic Requirements/Ageipelago Bari.xlsx
+++ b/docs/Logic Requirements/Ageipelago Bari.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/Logic Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{1D546BFC-1BE8-48DF-A905-3C802CA96E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{555E57BC-C3A5-4A21-9A93-35C4DAAB18AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FBDDD6-0A02-48BC-9AA0-3DA2E7C54880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Bari" sheetId="1" r:id="rId1"/>
+    <sheet name="Arrival at Bari" sheetId="2" r:id="rId2"/>
+    <sheet name="The Rebellion of Melus" sheetId="3" r:id="rId3"/>
+    <sheet name="Loose Ends" sheetId="4" r:id="rId4"/>
+    <sheet name="The Best Laid Plans" sheetId="5" r:id="rId5"/>
+    <sheet name="The Onrushing Tide" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="213">
   <si>
     <t>Scenario</t>
   </si>
@@ -894,131 +899,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Capua</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Potenza</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cannot be defeated in Vanilla, although if we delete the Horses in the left Corner after </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Melus' Garrison</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is defeated, we can kill whichever we didn't take over in the Beginning as a Location.
-The Player can only grab 1 of the 2 towns in Vanilla, but if they can get both as Items here, the Location for defeating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Malus' Garrison</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> wouldn't really work anymore. Maybe only give them the Resources and make '</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Misc. Buildings of whatever Town you enter first</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">' a seperate Item? 
-The Relic only spawn if the Player chooses </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Potenza</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, but we can just spawn it there anyways so the Player can get it regardless.</t>
-    </r>
-  </si>
-  <si>
     <t>6 Long Swordsmen, 5 Pikemen, 4 Crossbowmen
 1 Scout (Gaia)
 4 Long Swordsmen, 8 Pikemen, 4 Crossbowmen
@@ -3193,93 +3073,6 @@
       <t xml:space="preserve">
 Starting Units:
 Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-2 Monks
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-6 Long Swordsmen
-8 Pikemen
-10 Crossbowmen
-8 Knights
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-9 Long Swordsmen
-12 Pikemen
-10 Crossbowmen
-8 Knights
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-6 Long Swordsmen
-8 Pikemen
-10 Crossbowmen
-8 Knights</t>
     </r>
   </si>
   <si>
@@ -3656,12 +3449,814 @@
   <si>
     <t>Addittional Units spawned in while the Player is tasked to defend Bari</t>
   </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Camel Rider</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Genitour</t>
+  </si>
+  <si>
+    <t>Mameluke</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Demolition Ship</t>
+  </si>
+  <si>
+    <t>Fishing Boat</t>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Genoese Crossbowman</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Tent</t>
+  </si>
+  <si>
+    <t>Tent (Large)</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Barricade</t>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Heavy Camel Rider
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Heavy Cavalry Archer
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Byzantines research Town Watch and Town Patrol automatically</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mangonel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Huskarl</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>Elite Huskarl</t>
+  </si>
+  <si>
+    <t>Petard</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Capua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Potenza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cannot be defeated in Vanilla, although if we delete the Horses in the left Corner after </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Melus' Garrison</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is defeated, we can kill whichever we didn't take over in the Beginning as a Location.
+The Player can only grab 1 of the 2 towns in Vanilla, but if they can get both as Items here, the Location for defeating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Melus' Garrison</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> wouldn't really work anymore. Maybe only give them the Resources and make '</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Misc. Buildings of whatever Town you enter first</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">' a seperate Item? 
+The Relic only spawn if the Player chooses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Potenza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, but we can just spawn it there anyways so the Player can get it regardless.</t>
+    </r>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Fire Tower</t>
+  </si>
+  <si>
+    <t>Requires Base</t>
+  </si>
+  <si>
+    <t>No Bombard Tower</t>
+  </si>
+  <si>
+    <t>No Trade Cog
+No Transport Ship
+No Fire Ship
+No War Galley
+No Demolition Ship
+No Dromon
+No Bombard Cannon
+No Hand Cannoneer</t>
+  </si>
+  <si>
+    <t>Serjant</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Berserk</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Elite Berserk</t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>No Medium Warships
+No Heavy Warships
+No Careening
+No Dry Dock
+No Clinker Construction
+No Carvel Hull
+No Siphons
+No Bombard Tower
+No Spies
+Byzantines research  Town Patrol automatically</t>
+  </si>
+  <si>
+    <t>Byzantines research Town Patrol automatically
+No Bombard Tower</t>
+  </si>
+  <si>
+    <t>No Hand Cannoneer
+No Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Elite Genoese Crossbowman</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Teutonic Knight</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Tower</t>
+  </si>
+  <si>
+    <t>No Bombard Tower
+No Castle
+No Wonder</t>
+  </si>
+  <si>
+    <t>Norse Warrior</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Siege Tower</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>War Galley</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Requires Ships</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Stephanos Pateranos</t>
+  </si>
+  <si>
+    <t>Fast Fire Ship</t>
+  </si>
+  <si>
+    <t>Converts to Player</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+2 Monks
+1 Heavy Scorpion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+6 Long Swordsmen
+8 Pikemen
+10 Crossbowmen
+8 Knights
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+9 Long Swordsmen
+12 Pikemen
+10 Crossbowmen
+8 Knights
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+6 Long Swordsmen
+8 Pikemen
+10 Crossbowmen
+8 Knights</t>
+    </r>
+  </si>
+  <si>
+    <t>Pikemen</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>No Villager
+No Ships</t>
+  </si>
+  <si>
+    <t>Despawns in Vanilla</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>No Castle Age Unit Upgrades
+No Squires
+No Eco Techs
+No Dock Techs
+Arson
+Feudal Age Blacksmith Techs</t>
+  </si>
+  <si>
+    <t>Lumberyard</t>
+  </si>
+  <si>
+    <t>Shipyard</t>
+  </si>
+  <si>
+    <t>Sea Tower</t>
+  </si>
+  <si>
+    <t>Fortified Palisade Wall</t>
+  </si>
+  <si>
+    <t>Aqueduct</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Galley</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Galleon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elite Serjant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3803,6 +4398,67 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2FE2F5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3812,7 +4468,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3900,11 +4556,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3940,6 +4677,145 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4375,7 +5251,7 @@
         <v>22</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4383,13 +5259,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>33</v>
@@ -4398,32 +5274,32 @@
         <v>35</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="7" t="s">
+      <c r="O5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="Q5" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4431,33 +5307,33 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="10"/>
       <c r="J6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4465,45 +5341,45 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="Q7" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4511,49 +5387,49 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="I8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="408.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4578,4 +5454,2890 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CD0115-21D0-4090-BD99-F585F0E83BD6}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="G2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="G3" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K19" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="K28" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="L28" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A51F690-8687-45B6-8894-98CB495D74E8}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="G2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="G3" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F49EFB-3F6C-40CB-B621-4D13F92A8D94}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="G2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="G3" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="L24" s="39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F0931D8-471C-4FF0-846B-CC52910A462E}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="G2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="G3" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="43"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L27" s="39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="40"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE316F0-4714-4350-A166-61535B72B32D}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="G2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="G3" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="13"/>
+      <c r="G6" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="G7" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="G8" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="G9" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="G10" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="13"/>
+      <c r="G11" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="13"/>
+      <c r="G12" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="G13" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="13"/>
+      <c r="G14" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="G15" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="G16" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="54" t="s">
+        <v>204</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="L28" s="32" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="L31" s="32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L32" s="32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L33" s="32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="L34" s="35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Bari.xlsx
+++ b/docs/Logic Requirements/Ageipelago Bari.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FBDDD6-0A02-48BC-9AA0-3DA2E7C54880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FC6A29-CD59-4151-9150-8207A59FED8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="214">
   <si>
     <t>Scenario</t>
   </si>
@@ -3676,9 +3676,6 @@
     <t>Feudal - Castle Age</t>
   </si>
   <si>
-    <t>Byzantines research Town Watch and Town Patrol automatically</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="14"/>
@@ -3915,6 +3912,321 @@
   </si>
   <si>
     <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>No Hand Cannoneer
+No Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Elite Genoese Crossbowman</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Teutonic Knight</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Tower</t>
+  </si>
+  <si>
+    <t>No Bombard Tower
+No Castle
+No Wonder</t>
+  </si>
+  <si>
+    <t>Norse Warrior</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Siege Tower</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>War Galley</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Requires Ships</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Stephanos Pateranos</t>
+  </si>
+  <si>
+    <t>Fast Fire Ship</t>
+  </si>
+  <si>
+    <t>Converts to Player</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+2 Monks
+1 Heavy Scorpion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+6 Long Swordsmen
+8 Pikemen
+10 Crossbowmen
+8 Knights
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+9 Long Swordsmen
+12 Pikemen
+10 Crossbowmen
+8 Knights
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+6 Long Swordsmen
+8 Pikemen
+10 Crossbowmen
+8 Knights</t>
+    </r>
+  </si>
+  <si>
+    <t>Pikemen</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>No Villager
+No Ships</t>
+  </si>
+  <si>
+    <t>Despawns in Vanilla</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Lumberyard</t>
+  </si>
+  <si>
+    <t>Shipyard</t>
+  </si>
+  <si>
+    <t>Sea Tower</t>
+  </si>
+  <si>
+    <t>Fortified Palisade Wall</t>
+  </si>
+  <si>
+    <t>Aqueduct</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Galley</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Galleon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elite Serjant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Byzantines research Town Watch and Town Patrol automatically
+Man-at-Arms researched automatically</t>
   </si>
   <si>
     <t>No Medium Warships
@@ -3926,330 +4238,28 @@
 No Siphons
 No Bombard Tower
 No Spies
-Byzantines research  Town Patrol automatically</t>
+Byzantines research  Town Patrol automatically
+On Standard:
+Murder Holes and Ballistics are researched automatically</t>
   </si>
   <si>
     <t>Byzantines research Town Patrol automatically
-No Bombard Tower</t>
-  </si>
-  <si>
-    <t>No Hand Cannoneer
-No Bombard Cannon</t>
-  </si>
-  <si>
-    <t>Arbalester</t>
-  </si>
-  <si>
-    <t>Elite Genoese Crossbowman</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trebuchet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Not on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <t>Elite Teutonic Knight</t>
-  </si>
-  <si>
-    <t>Paladin</t>
-  </si>
-  <si>
-    <t>Throwing Axeman</t>
-  </si>
-  <si>
-    <t>Tower</t>
-  </si>
-  <si>
-    <t>No Bombard Tower
-No Castle
-No Wonder</t>
-  </si>
-  <si>
-    <t>Norse Warrior</t>
-  </si>
-  <si>
-    <t>Mangonel</t>
-  </si>
-  <si>
-    <t>Siege Tower</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>War Galley</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Not on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <t>Requires Ships</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trebuchet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Not on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <t>Stephanos Pateranos</t>
-  </si>
-  <si>
-    <t>Fast Fire Ship</t>
-  </si>
-  <si>
-    <t>Converts to Player</t>
-  </si>
-  <si>
-    <t>Heavy Scorpion</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-2 Monks
-1 Heavy Scorpion
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-6 Long Swordsmen
-8 Pikemen
-10 Crossbowmen
-8 Knights
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-9 Long Swordsmen
-12 Pikemen
-10 Crossbowmen
-8 Knights
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-6 Long Swordsmen
-8 Pikemen
-10 Crossbowmen
-8 Knights</t>
-    </r>
-  </si>
-  <si>
-    <t>Pikemen</t>
-  </si>
-  <si>
-    <t>Unavailable</t>
-  </si>
-  <si>
-    <t>No Villager
-No Ships</t>
-  </si>
-  <si>
-    <t>Despawns in Vanilla</t>
-  </si>
-  <si>
-    <t>Horse</t>
-  </si>
-  <si>
-    <t>No Castle Age Unit Upgrades
-No Squires
-No Eco Techs
-No Dock Techs
+No Bombard Tower
+On Standard:
+Murder Holes and Guard Tower are researched automatically</t>
+  </si>
+  <si>
+    <t>Byzantines research Town Patrol automatically
+No Bombard Tower
+On Standard:
+Murder Holes, Ballistics and Guard Tower are researched automatically</t>
+  </si>
+  <si>
+    <t>Squires, Pikeman, Long Swordsman, Light Cavalry,  Crossbowman, Elite Skirmisher and  Conscription are researched automatically
 Arson
-Feudal Age Blacksmith Techs</t>
-  </si>
-  <si>
-    <t>Lumberyard</t>
-  </si>
-  <si>
-    <t>Shipyard</t>
-  </si>
-  <si>
-    <t>Sea Tower</t>
-  </si>
-  <si>
-    <t>Fortified Palisade Wall</t>
-  </si>
-  <si>
-    <t>Aqueduct</t>
-  </si>
-  <si>
-    <t>Fence</t>
-  </si>
-  <si>
-    <t>Only on Hard Logic</t>
-  </si>
-  <si>
-    <t>Castle Age</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Galley</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Only on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Galleon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Only on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Elite Serjant</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Not on Standard)</t>
-    </r>
+Feudal Age Blacksmith Techs
+On Standard:
+ Ballistics is researched automatically</t>
   </si>
 </sst>
 </file>
@@ -4715,24 +4725,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4816,6 +4808,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5277,7 +5287,7 @@
         <v>36</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7" t="s">
@@ -5408,7 +5418,7 @@
         <v>68</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>74</v>
@@ -5468,11 +5478,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56"/>
       <c r="G2" s="2" t="s">
         <v>122</v>
       </c>
@@ -5487,18 +5497,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="57" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
       <c r="G3" s="24" t="s">
         <v>119</v>
       </c>
       <c r="H3" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="58" t="s">
+      <c r="K3" s="52" t="s">
         <v>136</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -5528,7 +5538,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
         <v>114</v>
       </c>
@@ -5536,7 +5546,7 @@
         <v>114</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>148</v>
+        <v>209</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>124</v>
@@ -5649,7 +5659,7 @@
       <c r="K11" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="L11" s="32" t="s">
+      <c r="L11" s="26" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5663,10 +5673,10 @@
       <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K12" s="46" t="s">
+      <c r="K12" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="L12" s="26" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5674,13 +5684,13 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="40" t="s">
         <v>145</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="54" t="s">
+      <c r="K13" s="48" t="s">
         <v>81</v>
       </c>
       <c r="L13" s="5" t="s">
@@ -5697,7 +5707,7 @@
       <c r="H14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="30" t="s">
         <v>99</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -5708,13 +5718,13 @@
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
-      <c r="G15" s="46" t="s">
+      <c r="G15" s="40" t="s">
         <v>126</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="30" t="s">
         <v>83</v>
       </c>
       <c r="L15" s="5" t="s">
@@ -5728,10 +5738,10 @@
       <c r="G16" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="K16" s="36" t="s">
+      <c r="K16" s="30" t="s">
         <v>139</v>
       </c>
       <c r="L16" s="5" t="s">
@@ -5742,10 +5752,10 @@
       <c r="G17" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="K17" s="36" t="s">
+      <c r="K17" s="30" t="s">
         <v>110</v>
       </c>
       <c r="L17" s="5" t="s">
@@ -5753,13 +5763,13 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="36" t="s">
+      <c r="K18" s="30" t="s">
         <v>88</v>
       </c>
       <c r="L18" s="5" t="s">
@@ -5767,13 +5777,13 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="K19" s="36" t="s">
+      <c r="K19" s="30" t="s">
         <v>87</v>
       </c>
       <c r="L19" s="5" t="s">
@@ -5781,27 +5791,27 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="36" t="s">
+      <c r="G20" s="30" t="s">
         <v>132</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="36" t="s">
-        <v>162</v>
+      <c r="K20" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="54" t="s">
+      <c r="G21" s="48" t="s">
         <v>133</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K21" s="36" t="s">
+      <c r="K21" s="30" t="s">
         <v>111</v>
       </c>
       <c r="L21" s="5" t="s">
@@ -5809,13 +5819,13 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="36" t="s">
+      <c r="G22" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="30" t="s">
         <v>105</v>
       </c>
       <c r="L22" s="5" t="s">
@@ -5823,13 +5833,13 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="54" t="s">
+      <c r="G23" s="48" t="s">
         <v>106</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="K23" s="31" t="s">
         <v>141</v>
       </c>
       <c r="L23" s="5" t="s">
@@ -5837,13 +5847,13 @@
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="36" t="s">
+      <c r="G24" s="30" t="s">
         <v>104</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K24" s="37" t="s">
+      <c r="K24" s="31" t="s">
         <v>142</v>
       </c>
       <c r="L24" s="5" t="s">
@@ -5851,7 +5861,7 @@
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="37" t="s">
+      <c r="G25" s="31" t="s">
         <v>97</v>
       </c>
       <c r="H25" s="5" t="s">
@@ -5860,12 +5870,12 @@
       <c r="K25" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="L25" s="32" t="s">
+      <c r="L25" s="26" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="38" t="s">
+      <c r="G26" s="32" t="s">
         <v>135</v>
       </c>
       <c r="H26" s="9" t="s">
@@ -5874,12 +5884,12 @@
       <c r="K26" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="32" t="s">
+      <c r="L26" s="26" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="31" t="s">
         <v>144</v>
       </c>
       <c r="H27" s="5" t="s">
@@ -5888,35 +5898,35 @@
       <c r="K27" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="L27" s="32" t="s">
+      <c r="L27" s="26" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
       <c r="K28" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="L28" s="32" t="s">
+      <c r="L28" s="26" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="13"/>
@@ -5996,11 +6006,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56"/>
       <c r="G2" s="2" t="s">
         <v>122</v>
       </c>
@@ -6015,19 +6025,19 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="G3" s="27" t="s">
         <v>119</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
       <c r="K3" s="23" t="s">
         <v>141</v>
       </c>
@@ -6045,14 +6055,14 @@
       <c r="D4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="25" t="s">
         <v>115</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
       <c r="K4" s="21" t="s">
         <v>142</v>
       </c>
@@ -6060,26 +6070,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>167</v>
-      </c>
       <c r="D5" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="G5" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="28" t="s">
         <v>113</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
       <c r="K5" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>80</v>
@@ -6089,14 +6099,14 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="41" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
       <c r="K6" s="21" t="s">
         <v>94</v>
       </c>
@@ -6108,38 +6118,38 @@
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="41" t="s">
         <v>102</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
       <c r="K7" s="21" t="s">
         <v>88</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="13"/>
-      <c r="G8" s="31" t="s">
-        <v>149</v>
+      <c r="G8" s="25" t="s">
+        <v>148</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="21" t="s">
         <v>87</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6147,13 +6157,13 @@
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
       <c r="G9" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
       <c r="K9" s="21" t="s">
         <v>101</v>
       </c>
@@ -6166,13 +6176,13 @@
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
       <c r="G10" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
       <c r="K10" s="21" t="s">
         <v>98</v>
       </c>
@@ -6190,8 +6200,8 @@
       <c r="H11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
       <c r="K11" s="21" t="s">
         <v>109</v>
       </c>
@@ -6204,13 +6214,13 @@
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
       <c r="G12" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
       <c r="K12" s="21" t="s">
         <v>103</v>
       </c>
@@ -6223,18 +6233,18 @@
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
       <c r="G13" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
       <c r="K13" s="21" t="s">
         <v>139</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -6242,13 +6252,13 @@
       <c r="C14" s="20"/>
       <c r="D14" s="13"/>
       <c r="G14" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="21" t="s">
         <v>96</v>
       </c>
@@ -6261,13 +6271,13 @@
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
       <c r="G15" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
       <c r="K15" s="21" t="s">
         <v>83</v>
       </c>
@@ -6279,35 +6289,35 @@
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
-      <c r="G16" s="46" t="s">
-        <v>156</v>
+      <c r="G16" s="40" t="s">
+        <v>155</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="46" t="s">
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G17" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="46" t="s">
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6317,29 +6327,29 @@
       <c r="H18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="36" t="s">
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="30" t="s">
         <v>143</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
       <c r="K19" s="16" t="s">
         <v>82</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6349,29 +6359,29 @@
       <c r="H20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
       <c r="K20" s="16" t="s">
         <v>99</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
       <c r="K21" s="16" t="s">
         <v>107</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6381,8 +6391,8 @@
       <c r="H22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
       <c r="K22" s="16" t="s">
         <v>110</v>
       </c>
@@ -6392,13 +6402,13 @@
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
       <c r="K23" s="16" t="s">
         <v>138</v>
       </c>
@@ -6413,10 +6423,10 @@
       <c r="H24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
       <c r="K24" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>80</v>
@@ -6429,8 +6439,8 @@
       <c r="H25" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
       <c r="K25" s="16" t="s">
         <v>112</v>
       </c>
@@ -6441,8 +6451,8 @@
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
       <c r="K26" s="16" t="s">
         <v>105</v>
       </c>
@@ -6453,8 +6463,8 @@
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
       <c r="K27" s="14" t="s">
         <v>111</v>
       </c>
@@ -6465,13 +6475,13 @@
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
       <c r="K28" s="17" t="s">
         <v>85</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6579,11 +6589,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56"/>
       <c r="G2" s="2" t="s">
         <v>122</v>
       </c>
@@ -6598,20 +6608,20 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="G3" s="42" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="G3" s="36" t="s">
         <v>100</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="42" t="s">
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="36" t="s">
         <v>94</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -6629,29 +6639,29 @@
         <v>116</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
       <c r="K4" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>176</v>
-      </c>
       <c r="D5" s="22" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>102</v>
@@ -6659,8 +6669,8 @@
       <c r="H5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
       <c r="K5" s="16" t="s">
         <v>141</v>
       </c>
@@ -6673,13 +6683,13 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
       <c r="K6" s="16" t="s">
         <v>142</v>
       </c>
@@ -6697,10 +6707,10 @@
       <c r="H7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
       <c r="K7" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>80</v>
@@ -6710,14 +6720,14 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="13"/>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="30" t="s">
         <v>104</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="16" t="s">
         <v>98</v>
       </c>
@@ -6729,14 +6739,14 @@
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="30" t="s">
         <v>86</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
       <c r="K9" s="16" t="s">
         <v>83</v>
       </c>
@@ -6748,14 +6758,14 @@
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
-      <c r="G10" s="36" t="s">
-        <v>150</v>
+      <c r="G10" s="30" t="s">
+        <v>149</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
       <c r="K10" s="16" t="s">
         <v>139</v>
       </c>
@@ -6767,14 +6777,14 @@
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="13"/>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="30" t="s">
         <v>124</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
       <c r="K11" s="16" t="s">
         <v>110</v>
       </c>
@@ -6786,15 +6796,15 @@
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="36" t="s">
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="30" t="s">
         <v>107</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -6805,15 +6815,15 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="G13" s="36" t="s">
-        <v>159</v>
+      <c r="G13" s="30" t="s">
+        <v>158</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="36" t="s">
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="30" t="s">
         <v>101</v>
       </c>
       <c r="L13" s="5" t="s">
@@ -6824,15 +6834,15 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="13"/>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="30" t="s">
         <v>95</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="36" t="s">
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="30" t="s">
         <v>112</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -6843,15 +6853,15 @@
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
-      <c r="G15" s="31" t="s">
-        <v>169</v>
+      <c r="G15" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="36" t="s">
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="30" t="s">
         <v>88</v>
       </c>
       <c r="L15" s="5" t="s">
@@ -6862,95 +6872,95 @@
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
-      <c r="G16" s="53" t="s">
+      <c r="G16" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="37" t="s">
+      <c r="H17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="53" t="s">
-        <v>172</v>
-      </c>
       <c r="H21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="36" t="s">
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="30" t="s">
         <v>109</v>
       </c>
       <c r="L21" s="5" t="s">
@@ -6958,15 +6968,15 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="37" t="s">
-        <v>151</v>
+      <c r="G22" s="31" t="s">
+        <v>150</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="36" t="s">
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="30" t="s">
         <v>96</v>
       </c>
       <c r="L22" s="5" t="s">
@@ -6974,15 +6984,15 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="37" t="s">
-        <v>157</v>
+      <c r="G23" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="36" t="s">
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="30" t="s">
         <v>103</v>
       </c>
       <c r="L23" s="5" t="s">
@@ -6990,46 +7000,46 @@
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="48" t="s">
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="L24" s="39" t="s">
+      <c r="L24" s="33" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="43"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="13"/>
@@ -7136,11 +7146,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56"/>
       <c r="G2" s="2" t="s">
         <v>122</v>
       </c>
@@ -7155,20 +7165,20 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="G3" s="27" t="s">
         <v>119</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="49" t="s">
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="43" t="s">
         <v>101</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -7185,40 +7195,40 @@
       <c r="D4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="25" t="s">
         <v>115</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="36" t="s">
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="30" t="s">
         <v>109</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="G5" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>97</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="36" t="s">
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="30" t="s">
         <v>103</v>
       </c>
       <c r="L5" s="5" t="s">
@@ -7229,15 +7239,15 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
-      <c r="G6" s="36" t="s">
-        <v>154</v>
+      <c r="G6" s="30" t="s">
+        <v>153</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="36" t="s">
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="30" t="s">
         <v>99</v>
       </c>
       <c r="L6" s="5" t="s">
@@ -7248,16 +7258,16 @@
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
-      <c r="G7" s="36" t="s">
-        <v>155</v>
+      <c r="G7" s="30" t="s">
+        <v>154</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="36" t="s">
-        <v>162</v>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>80</v>
@@ -7267,15 +7277,15 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="13"/>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="30" t="s">
         <v>108</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="36" t="s">
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="30" t="s">
         <v>141</v>
       </c>
       <c r="L8" s="5" t="s">
@@ -7286,15 +7296,15 @@
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="30" t="s">
         <v>89</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="36" t="s">
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="30" t="s">
         <v>142</v>
       </c>
       <c r="L9" s="5" t="s">
@@ -7305,15 +7315,15 @@
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="30" t="s">
         <v>104</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="36" t="s">
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="30" t="s">
         <v>92</v>
       </c>
       <c r="L10" s="5" t="s">
@@ -7324,15 +7334,15 @@
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="13"/>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="30" t="s">
         <v>95</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="36" t="s">
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="30" t="s">
         <v>138</v>
       </c>
       <c r="L11" s="5" t="s">
@@ -7349,9 +7359,9 @@
       <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="36" t="s">
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="30" t="s">
         <v>105</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -7362,16 +7372,16 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="G13" s="46" t="s">
-        <v>177</v>
+      <c r="G13" s="40" t="s">
+        <v>174</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="54" t="s">
-        <v>183</v>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="48" t="s">
+        <v>180</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>80</v>
@@ -7381,14 +7391,14 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="13"/>
-      <c r="G14" s="46" t="s">
-        <v>178</v>
+      <c r="G14" s="40" t="s">
+        <v>175</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="21" t="s">
         <v>83</v>
       </c>
@@ -7406,8 +7416,8 @@
       <c r="H15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
       <c r="K15" s="21" t="s">
         <v>88</v>
       </c>
@@ -7420,13 +7430,13 @@
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
       <c r="G16" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
       <c r="K16" s="21" t="s">
         <v>87</v>
       </c>
@@ -7435,16 +7445,16 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="31" t="s">
-        <v>179</v>
+      <c r="G17" s="25" t="s">
+        <v>176</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
       <c r="K17" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>80</v>
@@ -7452,13 +7462,13 @@
     </row>
     <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G18" s="19" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
       <c r="K18" s="21" t="s">
         <v>96</v>
       </c>
@@ -7468,13 +7478,13 @@
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
       <c r="K19" s="21" t="s">
         <v>82</v>
       </c>
@@ -7484,13 +7494,13 @@
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="19" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
       <c r="K20" s="21" t="s">
         <v>107</v>
       </c>
@@ -7500,13 +7510,13 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
       <c r="K21" s="21" t="s">
         <v>139</v>
       </c>
@@ -7515,14 +7525,14 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="37" t="s">
+      <c r="G22" s="31" t="s">
         <v>100</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
       <c r="K22" s="17" t="s">
         <v>85</v>
       </c>
@@ -7531,14 +7541,14 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="37" t="s">
+      <c r="G23" s="31" t="s">
         <v>93</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
       <c r="K23" s="17" t="s">
         <v>143</v>
       </c>
@@ -7547,14 +7557,14 @@
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="55" t="s">
-        <v>182</v>
+      <c r="G24" s="49" t="s">
+        <v>179</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
       <c r="K24" s="17" t="s">
         <v>90</v>
       </c>
@@ -7563,14 +7573,14 @@
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="37" t="s">
-        <v>171</v>
+      <c r="G25" s="31" t="s">
+        <v>170</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="45"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="39"/>
       <c r="K25" s="17" t="s">
         <v>98</v>
       </c>
@@ -7581,8 +7591,8 @@
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
       <c r="K26" s="17" t="s">
         <v>111</v>
       </c>
@@ -7593,38 +7603,38 @@
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
       <c r="K27" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="L27" s="39" t="s">
+      <c r="L27" s="33" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="13"/>
@@ -7713,11 +7723,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56"/>
       <c r="G2" s="2" t="s">
         <v>122</v>
       </c>
@@ -7732,20 +7742,20 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="G3" s="33" t="s">
+      <c r="B3" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="G3" s="27" t="s">
         <v>119</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="52" t="s">
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="46" t="s">
         <v>107</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -7762,40 +7772,40 @@
       <c r="D4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="25" t="s">
         <v>115</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="50" t="s">
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="44" t="s">
         <v>96</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="G5" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>106</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="50" t="s">
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="44" t="s">
         <v>83</v>
       </c>
       <c r="L5" s="5" t="s">
@@ -7806,15 +7816,15 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="44" t="s">
         <v>93</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="50" t="s">
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="44" t="s">
         <v>98</v>
       </c>
       <c r="L6" s="5" t="s">
@@ -7825,15 +7835,15 @@
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
-      <c r="G7" s="56" t="s">
-        <v>185</v>
+      <c r="G7" s="50" t="s">
+        <v>182</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="50" t="s">
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="44" t="s">
         <v>101</v>
       </c>
       <c r="L7" s="5" t="s">
@@ -7844,15 +7854,15 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="13"/>
-      <c r="G8" s="50" t="s">
-        <v>157</v>
+      <c r="G8" s="44" t="s">
+        <v>156</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="50" t="s">
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="44" t="s">
         <v>109</v>
       </c>
       <c r="L8" s="5" t="s">
@@ -7863,15 +7873,15 @@
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="13"/>
-      <c r="G9" s="50" t="s">
-        <v>186</v>
+      <c r="G9" s="44" t="s">
+        <v>183</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="50" t="s">
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="44" t="s">
         <v>105</v>
       </c>
       <c r="L9" s="5" t="s">
@@ -7882,15 +7892,15 @@
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="13"/>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="44" t="s">
         <v>86</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="50" t="s">
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="44" t="s">
         <v>141</v>
       </c>
       <c r="L10" s="5" t="s">
@@ -7901,15 +7911,15 @@
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="13"/>
-      <c r="G11" s="50" t="s">
-        <v>158</v>
+      <c r="G11" s="44" t="s">
+        <v>157</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="50" t="s">
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="44" t="s">
         <v>142</v>
       </c>
       <c r="L11" s="5" t="s">
@@ -7920,16 +7930,16 @@
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="13"/>
-      <c r="G12" s="56" t="s">
-        <v>187</v>
+      <c r="G12" s="50" t="s">
+        <v>184</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="56" t="s">
-        <v>202</v>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="50" t="s">
+        <v>198</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>80</v>
@@ -7939,15 +7949,15 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
-      <c r="G13" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="50" t="s">
+      <c r="G13" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="44" t="s">
         <v>92</v>
       </c>
       <c r="L13" s="5" t="s">
@@ -7958,15 +7968,15 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="13"/>
-      <c r="G14" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="50" t="s">
+      <c r="G14" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="44" t="s">
         <v>94</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -7977,16 +7987,16 @@
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="H15" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="56" t="s">
-        <v>183</v>
+      <c r="H15" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="50" t="s">
+        <v>180</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>80</v>
@@ -8002,10 +8012,10 @@
       <c r="H16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="50" t="s">
-        <v>173</v>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="44" t="s">
+        <v>172</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>80</v>
@@ -8013,14 +8023,14 @@
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G17" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="36" t="s">
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="30" t="s">
         <v>138</v>
       </c>
       <c r="L17" s="5" t="s">
@@ -8034,10 +8044,10 @@
       <c r="H18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="54" t="s">
-        <v>203</v>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="48" t="s">
+        <v>199</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>80</v>
@@ -8045,15 +8055,15 @@
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="54" t="s">
-        <v>204</v>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="48" t="s">
+        <v>200</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>80</v>
@@ -8061,13 +8071,13 @@
     </row>
     <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G20" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
       <c r="K20" s="17" t="s">
         <v>88</v>
       </c>
@@ -8082,8 +8092,8 @@
       <c r="H21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
       <c r="K21" s="17" t="s">
         <v>87</v>
       </c>
@@ -8092,14 +8102,14 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="31" t="s">
-        <v>190</v>
+      <c r="G22" s="25" t="s">
+        <v>187</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
       <c r="K22" s="17" t="s">
         <v>90</v>
       </c>
@@ -8114,8 +8124,8 @@
       <c r="H23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
       <c r="K23" s="17" t="s">
         <v>82</v>
       </c>
@@ -8125,13 +8135,13 @@
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
       <c r="K24" s="17" t="s">
         <v>110</v>
       </c>
@@ -8140,14 +8150,14 @@
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="51" t="s">
-        <v>196</v>
+      <c r="G25" s="45" t="s">
+        <v>193</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
       <c r="K25" s="17" t="s">
         <v>111</v>
       </c>
@@ -8156,60 +8166,60 @@
       </c>
     </row>
     <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G26" s="57" t="s">
-        <v>191</v>
+      <c r="G26" s="51" t="s">
+        <v>188</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
+        <v>196</v>
+      </c>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
       <c r="K26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="L26" s="32" t="s">
-        <v>193</v>
+      <c r="L26" s="26" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L27" s="32" t="s">
-        <v>193</v>
+        <v>189</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="H28" s="32" t="s">
-        <v>193</v>
+      <c r="H28" s="26" t="s">
+        <v>190</v>
       </c>
       <c r="K28" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="L28" s="32" t="s">
-        <v>193</v>
+      <c r="L28" s="26" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>193</v>
+      <c r="G29" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>190</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>80</v>
@@ -8223,43 +8233,43 @@
         <v>80</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="44" t="s">
+      <c r="G31" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="H31" s="39" t="s">
+      <c r="H31" s="33" t="s">
         <v>80</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="L31" s="32" t="s">
-        <v>208</v>
+        <v>161</v>
+      </c>
+      <c r="L31" s="26" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>80</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="L32" s="32" t="s">
-        <v>208</v>
+        <v>162</v>
+      </c>
+      <c r="L32" s="26" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G33" s="19" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>80</v>
@@ -8267,13 +8277,13 @@
       <c r="K33" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>208</v>
+      <c r="L33" s="26" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G34" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>80</v>
@@ -8281,21 +8291,21 @@
       <c r="K34" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="L34" s="35" t="s">
-        <v>208</v>
+      <c r="L34" s="29" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G37" s="13"/>
